--- a/output/pdf_financials_xlsx/PTM.xlsx
+++ b/output/pdf_financials_xlsx/PTM.xlsx
@@ -1332,37 +1332,37 @@
         <v>-10.25</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>6.857</v>
+        <v>-1.087</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>80.79600000000001</v>
+        <v>7.494</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1179.087</v>
+        <v>-1.655</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>82.048</v>
+        <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>33.446</v>
+        <v>-0.106</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>14.184</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>26.071</v>
+        <v>-0.055</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>16.493</v>
+        <v>0.007</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>11.284</v>
+        <v>-0.042</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>9.183</v>
+        <v>-0.031</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>9.055999999999999</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="17">
@@ -1650,37 +1650,37 @@
         <v>-10.459</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.972</v>
+        <v>-3.972</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>36.651</v>
+        <v>-36.651</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>590.371</v>
+        <v>-590.371</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>41.024</v>
+        <v>-41.024</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>16.776</v>
+        <v>-16.776</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>7.128</v>
+        <v>-7.128</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>13.063</v>
+        <v>-13.063</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>8.243</v>
+        <v>-8.243</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>5.663</v>
+        <v>-5.663</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>4.607</v>
+        <v>-4.607</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>4.537</v>
+        <v>-4.537</v>
       </c>
     </row>
     <row r="21">
@@ -1835,37 +1835,37 @@
         <v>-10.459</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3.972</v>
+        <v>-3.972</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>36.651</v>
+        <v>-36.651</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>590.371</v>
+        <v>-590.371</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>41.024</v>
+        <v>-41.024</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>16.776</v>
+        <v>-16.776</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>7.128</v>
+        <v>-7.128</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>13.063</v>
+        <v>-13.063</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.243</v>
+        <v>-8.243</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.663</v>
+        <v>-5.663</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>4.607</v>
+        <v>-4.607</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>4.537</v>
+        <v>-4.537</v>
       </c>
     </row>
     <row r="24">
@@ -2030,37 +2030,37 @@
         <v>522.95</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>79.44</v>
+        <v>-79.44</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>140.965385</v>
+        <v>-140.965385</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>13.716798</v>
+        <v>-13.716798</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>20.208867</v>
+        <v>-20.208867</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>32.261538</v>
+        <v>-32.261538</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>64.8</v>
+        <v>-64.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>72.572222</v>
+        <v>-72.572222</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>91.58888899999999</v>
+        <v>-91.58888899999999</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>94.38333299999999</v>
+        <v>-94.38333299999999</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>92.14</v>
+        <v>-92.14</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>113.425</v>
+        <v>-113.425</v>
       </c>
     </row>
     <row r="27">
@@ -2093,37 +2093,37 @@
         <v>-14.136</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>10.638</v>
+        <v>2.694</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>81.929</v>
+        <v>8.627000000000001</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1180.149</v>
+        <v>-0.593</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>82.78700000000001</v>
+        <v>0.739</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>33.81</v>
+        <v>0.258</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>14.342</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>26.168</v>
+        <v>0.042</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>16.669</v>
+        <v>0.183</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>11.284</v>
+        <v>-0.042</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>9.183</v>
+        <v>-0.031</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>9.055999999999999</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="28">
@@ -2217,37 +2217,37 @@
         <v>-13.662</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.156</v>
+        <v>3.212</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>82.375</v>
+        <v>9.073</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1180.684</v>
+        <v>-0.058</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>83.134</v>
+        <v>1.086</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>34.045</v>
+        <v>0.493</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.519</v>
+        <v>0.263</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>26.29</v>
+        <v>0.164</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>16.76</v>
+        <v>0.274</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>11.367</v>
+        <v>0.041</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>9.255000000000001</v>
+        <v>0.041</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>9.124000000000001</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="30">
@@ -2377,37 +2377,39 @@
         <v>-2.039024390243902</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>42.07379320402509</v>
+        <v>-265.409383624655</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>54.6376058220704</v>
+        <v>589.0712570056045</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>49.92981857996908</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>50</v>
+        <v>-35571.96374622356</v>
+      </c>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>49.84153560963942</v>
+        <v>-15726.41509433962</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>49.74619289340102</v>
+        <v>-9800</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>49.8945188140079</v>
+        <v>-23650.90909090909</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>50.02122112411326</v>
+        <v>117857.1428571429</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>49.81389578163772</v>
+        <v>-13383.33333333333</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>49.83120984427747</v>
+        <v>-14761.29032258065</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>49.90061837455831</v>
+        <v>-25105.55555555555</v>
       </c>
     </row>
     <row r="32">
@@ -45117,13 +45119,13 @@
         </is>
       </c>
       <c r="T352" s="5" t="n">
-        <v>5.663</v>
+        <v>-5.663</v>
       </c>
       <c r="U352" s="5" t="n">
-        <v>4.607</v>
+        <v>-4.607</v>
       </c>
       <c r="V352" s="5" t="n">
-        <v>4.537</v>
+        <v>-4.537</v>
       </c>
     </row>
     <row r="353">
@@ -45315,19 +45317,19 @@
         </is>
       </c>
       <c r="R354" s="5" t="n">
-        <v>8.164999999999999</v>
+        <v>-8.164999999999999</v>
       </c>
       <c r="S354" s="5" t="n">
-        <v>15.172</v>
+        <v>-15.172</v>
       </c>
       <c r="T354" s="5" t="n">
-        <v>9.845000000000001</v>
+        <v>-9.845000000000001</v>
       </c>
       <c r="U354" s="5" t="n">
-        <v>1.985</v>
+        <v>-1.985</v>
       </c>
       <c r="V354" s="5" t="n">
-        <v>4.364</v>
+        <v>-4.364</v>
       </c>
     </row>
     <row r="355">
@@ -47201,13 +47203,13 @@
         </is>
       </c>
       <c r="R373" s="5" t="n">
-        <v>13.063</v>
+        <v>-13.063</v>
       </c>
       <c r="S373" s="5" t="n">
-        <v>8.243</v>
+        <v>-8.243</v>
       </c>
       <c r="T373" s="5" t="n">
-        <v>5.663</v>
+        <v>-5.663</v>
       </c>
       <c r="U373" t="inlineStr">
         <is>
@@ -48505,22 +48507,22 @@
         </is>
       </c>
       <c r="N386" s="5" t="n">
-        <v>590.371</v>
+        <v>-590.371</v>
       </c>
       <c r="O386" s="5" t="n">
-        <v>41.024</v>
+        <v>-41.024</v>
       </c>
       <c r="P386" s="5" t="n">
-        <v>16.776</v>
+        <v>-16.776</v>
       </c>
       <c r="Q386" s="5" t="n">
-        <v>7.128</v>
+        <v>-7.128</v>
       </c>
       <c r="R386" s="5" t="n">
-        <v>13.063</v>
+        <v>-13.063</v>
       </c>
       <c r="S386" s="5" t="n">
-        <v>8.243</v>
+        <v>-8.243</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -48707,22 +48709,22 @@
         </is>
       </c>
       <c r="N388" s="5" t="n">
-        <v>531.285</v>
+        <v>-531.285</v>
       </c>
       <c r="O388" s="5" t="n">
-        <v>19.147</v>
+        <v>-19.147</v>
       </c>
       <c r="P388" s="5" t="n">
-        <v>16.671</v>
+        <v>-16.671</v>
       </c>
       <c r="Q388" s="5" t="n">
-        <v>11.615</v>
+        <v>-11.615</v>
       </c>
       <c r="R388" s="5" t="n">
-        <v>8.164999999999999</v>
+        <v>-8.164999999999999</v>
       </c>
       <c r="S388" s="5" t="n">
-        <v>15.172</v>
+        <v>-15.172</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -49755,13 +49757,13 @@
         </is>
       </c>
       <c r="P398" s="5" t="n">
-        <v>16.776</v>
+        <v>-16.776</v>
       </c>
       <c r="Q398" s="5" t="n">
-        <v>7.128</v>
+        <v>-7.128</v>
       </c>
       <c r="R398" s="5" t="n">
-        <v>13.063</v>
+        <v>-13.063</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
@@ -49959,13 +49961,13 @@
         </is>
       </c>
       <c r="P400" s="5" t="n">
-        <v>16.671</v>
+        <v>-16.671</v>
       </c>
       <c r="Q400" s="5" t="n">
-        <v>11.615</v>
+        <v>-11.615</v>
       </c>
       <c r="R400" s="5" t="n">
-        <v>8.164999999999999</v>
+        <v>-8.164999999999999</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -53564,13 +53566,13 @@
         </is>
       </c>
       <c r="M435" s="5" t="n">
-        <v>36.651</v>
+        <v>-36.651</v>
       </c>
       <c r="N435" s="5" t="n">
-        <v>590.371</v>
+        <v>-590.371</v>
       </c>
       <c r="O435" s="5" t="n">
-        <v>41.024</v>
+        <v>-41.024</v>
       </c>
       <c r="P435" t="inlineStr">
         <is>
@@ -53872,13 +53874,13 @@
         <v>-13.739</v>
       </c>
       <c r="M438" s="5" t="n">
-        <v>86.681</v>
+        <v>-86.681</v>
       </c>
       <c r="N438" s="5" t="n">
-        <v>531.285</v>
+        <v>-531.285</v>
       </c>
       <c r="O438" s="5" t="n">
-        <v>19.147</v>
+        <v>-19.147</v>
       </c>
       <c r="P438" t="inlineStr">
         <is>
@@ -54925,13 +54927,13 @@
         </is>
       </c>
       <c r="L448" s="5" t="n">
-        <v>3.972</v>
+        <v>-3.972</v>
       </c>
       <c r="M448" s="5" t="n">
-        <v>36.651</v>
+        <v>-36.651</v>
       </c>
       <c r="N448" s="5" t="n">
-        <v>590.371</v>
+        <v>-590.371</v>
       </c>
       <c r="O448" t="inlineStr">
         <is>
@@ -56083,10 +56085,10 @@
         </is>
       </c>
       <c r="L459" s="5" t="n">
-        <v>3.972</v>
+        <v>-3.972</v>
       </c>
       <c r="M459" s="5" t="n">
-        <v>36.651</v>
+        <v>-36.651</v>
       </c>
       <c r="N459" t="inlineStr">
         <is>
@@ -56295,10 +56297,10 @@
         </is>
       </c>
       <c r="L461" s="5" t="n">
-        <v>104.373</v>
+        <v>-104.373</v>
       </c>
       <c r="M461" s="5" t="n">
-        <v>86.681</v>
+        <v>-86.681</v>
       </c>
       <c r="N461" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PTM.xlsx
+++ b/output/pdf_financials_xlsx/PTM.xlsx
@@ -1110,7 +1110,7 @@
         <v>-0.176</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.584</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>0.183</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.042</v>
+        <v>0.542</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-0.031</v>
@@ -2241,7 +2241,7 @@
         <v>0.274</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.041</v>
+        <v>0.625</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>0.041</v>
@@ -2555,16 +2555,16 @@
         <v>3.414</v>
       </c>
       <c r="L34" s="3" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="M34" s="3" t="n">
         <v>3.017</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.308</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>6.059</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>12.33</v>
@@ -2681,16 +2681,16 @@
         <v>3.414</v>
       </c>
       <c r="L36" s="3" t="n">
+        <v>12.634</v>
+      </c>
+      <c r="M36" s="3" t="n">
         <v>10.101</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>7.084</v>
-      </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.308</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>6.059</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>12.33</v>
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.369</v>
+        <v>0.352</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.693</v>
+        <v>0.385</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>6.343</v>
+        <v>0.284</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.052</v>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -46816,7 +46816,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
